--- a/output/pdf_financials_xlsx/DM.xlsx
+++ b/output/pdf_financials_xlsx/DM.xlsx
@@ -5114,16 +5114,16 @@
         <v>-0.017293</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-0.001745</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-0.023252</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>-0.054562</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>-0.077288</v>
       </c>
     </row>
     <row r="92">
@@ -5163,16 +5163,16 @@
         <v>5.249497</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.310314999999999</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>8.149978000000001</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.993180000000001</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>9.649138000000001</v>
       </c>
     </row>
     <row r="93">
@@ -9156,7 +9156,11 @@
           <t>Reserves (note 12)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -9240,7 +9244,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11086,7 +11094,11 @@
           <t>Reserves (note 11)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -11170,7 +11182,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -12870,7 +12886,11 @@
           <t>Reserves (note 10)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -16576,7 +16596,11 @@
           <t>Reserves (note 11)</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DM.xlsx
+++ b/output/pdf_financials_xlsx/DM.xlsx
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.175075</v>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.175075</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.102123</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1905,7 +1905,7 @@
         <v>11.765794</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-16.270217</v>
+        <v>-16.37234</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-25.777682</v>
@@ -2015,7 +2015,7 @@
         <v>13.277498</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-13.478339</v>
+        <v>-13.580462</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-22.173771</v>
@@ -2074,7 +2074,7 @@
         <v>27.0808851244079</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-44.20730744352895</v>
+        <v>-44.54225842362045</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>-252.4316290739942</v>
@@ -2211,22 +2211,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.499432</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.433203</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.379103</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.326003</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.235703</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.40434</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>2.90629</v>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.499432</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.433203</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.379103</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.326003</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.235703</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.40434</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>2.90629</v>
@@ -2912,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.403749</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.544898</v>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -19290,7 +19290,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
@@ -52756,7 +52756,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">

--- a/output/pdf_financials_xlsx/DM.xlsx
+++ b/output/pdf_financials_xlsx/DM.xlsx
@@ -5498,31 +5498,31 @@
         <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.000155</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.084091</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>2.835109</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.7659899999999999</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.729994</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1.46687</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>2.567072</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>2.847794</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.768541</v>
       </c>
     </row>
     <row r="101">
@@ -6098,7 +6098,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.001475</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.570899</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -20154,7 +20154,11 @@
           <t>Depreciation of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -20240,7 +20244,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -24744,7 +24748,11 @@
           <t>Depreciation of property and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -24830,7 +24838,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -27482,7 +27490,11 @@
           <t>Depreciation of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -27568,7 +27580,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -30314,7 +30326,11 @@
           <t>Depreciation of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -30400,7 +30416,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -30908,7 +30924,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -31684,7 +31704,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -32796,7 +32820,11 @@
           <t>Depreciation of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -32882,7 +32910,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -33478,7 +33506,11 @@
           <t>Loss on disposal of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -34670,7 +34702,11 @@
           <t>Depreciation of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -34756,7 +34792,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -37568,7 +37604,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -37652,7 +37692,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -43466,7 +43506,11 @@
           <t>Issuance of common shares (net of issuance costs)</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E423" s="5" t="n">
         <v>0.570899</v>
       </c>

--- a/output/pdf_financials_xlsx/DM.xlsx
+++ b/output/pdf_financials_xlsx/DM.xlsx
@@ -1252,7 +1252,7 @@
         <v>-25.777682</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-5.925407</v>
+        <v>-1.117165</v>
       </c>
     </row>
     <row r="17">
@@ -1295,19 +1295,19 @@
         <v>0.27775</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-2.67567</v>
+        <v>2.67567</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0.988592</v>
+        <v>0.988592</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>26.020826</v>
+        <v>-1.874741</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>2.863254</v>
+        <v>-1.944988</v>
       </c>
     </row>
     <row r="18">
@@ -1513,10 +1513,10 @@
         <v>-17.258809</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-24.245558</v>
+        <v>-24.146085</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-3.062153</v>
+        <v>-0.918266</v>
       </c>
     </row>
     <row r="21">
@@ -1911,7 +1911,7 @@
         <v>-25.777682</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-5.925407</v>
+        <v>-1.117165</v>
       </c>
     </row>
     <row r="28">
@@ -2021,7 +2021,7 @@
         <v>-22.173771</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.565748</v>
+        <v>0.242494</v>
       </c>
     </row>
     <row r="30">
@@ -2080,7 +2080,7 @@
         <v>-252.4316290739942</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-70.37577435350441</v>
+        <v>3.737767179896635</v>
       </c>
     </row>
     <row r="31">
@@ -2132,10 +2132,10 @@
         <v>-6.076083680998232</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-100.943234539087</v>
+        <v>-7.272729177123064</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-48.32164271585057</v>
+        <v>-174.1003343284117</v>
       </c>
     </row>
     <row r="32">
@@ -2391,13 +2391,13 @@
         <v>0</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0</v>
+        <v>2.661745</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>0.501074</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0</v>
+        <v>1.69387</v>
       </c>
     </row>
     <row r="38">
@@ -2587,13 +2587,13 @@
         <v>0</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0</v>
+        <v>2.661745</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>0.501074</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0</v>
+        <v>1.69387</v>
       </c>
     </row>
     <row r="42">
@@ -2930,13 +2930,13 @@
         <v>5.789824</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>6.205482</v>
+        <v>3.543737</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.398916</v>
+        <v>1.897842</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.77389</v>
+        <v>1.08002</v>
       </c>
     </row>
     <row r="49">
@@ -3879,16 +3879,16 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0535</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.045033</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.00902</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -3928,7 +3928,7 @@
         <v>0</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>0.0535</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>0.04949</v>
@@ -5535,13 +5535,13 @@
         <v>-0.004868</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>6.8e-05</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.020954</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.01312</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0.001605</v>
@@ -5780,13 +5780,13 @@
         <v>-0.004868</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>6.8e-05</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.00401</v>
+        <v>-0.024964</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.014205</v>
+        <v>0.001085</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>-0.0519</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.038214</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-0.43</v>
       </c>
       <c r="N114" s="3" t="n">
         <v>0</v>
@@ -6251,13 +6251,13 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.0791</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.241783</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.236577</v>
       </c>
     </row>
     <row r="116">
@@ -6282,13 +6282,13 @@
         <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-1e-05</v>
       </c>
       <c r="H116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-2.073219</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>0</v>
@@ -6551,10 +6551,10 @@
         <v>0</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-2.368397</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-1.210677</v>
       </c>
       <c r="O121" s="3" t="n">
         <v>0</v>
@@ -22288,7 +22288,11 @@
           <t>Proceeds from the sale of marketable securities (note 11)</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -23062,7 +23066,11 @@
           <t>Proceeds from private placement (note 12)</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -23146,7 +23154,11 @@
           <t>Shares repurchased (note 12)</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -26036,7 +26048,11 @@
           <t>Proceeds from the sale of marketable securities (note 10)</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -26120,7 +26136,11 @@
           <t>Purchase of marketable securities (note 10)</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -26712,7 +26732,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -26882,7 +26906,11 @@
           <t>Shares repurchased (note 11)</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -29036,7 +29064,11 @@
           <t>Proceeds from the sale of marketable securities (note 9)</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -29122,7 +29154,11 @@
           <t>Purchase of marketable securities (note 9)</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -29720,7 +29756,11 @@
           <t>Shares repurchased (note 10)</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -30242,7 +30282,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -33248,7 +33292,11 @@
           <t>Accretion expenses</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -34280,7 +34328,11 @@
           <t>Net proceeds from issuance of private placement</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -36240,7 +36292,11 @@
           <t>Purchase of intangible assets (note 5)</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -36754,7 +36810,11 @@
           <t>Net proceeds from issuance of private placement (note 10)</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -38806,7 +38866,11 @@
           <t>Purchase of intangible assets (note 8)</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -39328,7 +39392,11 @@
           <t>Net proceeds from issuance of private placement (note 12)</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -40108,7 +40176,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -42022,7 +42094,11 @@
           <t>HST Receivable</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -42632,7 +42708,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -46420,7 +46500,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
           <t>-</t>
@@ -46502,7 +46586,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
@@ -53394,7 +53482,11 @@
           <t>Income tax recovery (expense) total</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
           <t>-</t>
